--- a/CX-Survey-Analyzer/ai_analysis.xlsx
+++ b/CX-Survey-Analyzer/ai_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>advisor expertise and trust</t>
+          <t>advisor professionalism and responsiveness</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,14 +446,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>My advisor was extremely knowledgeable. | I trust my advisor.</t>
+          <t>My advisor was extremely knowledgeable. | The advisor responded quickly.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>advisor responsiveness</t>
+          <t>trust in advisor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -463,24 +463,58 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The advisor responded quickly.</t>
+          <t>I trust my advisor.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>digital experience usability</t>
+          <t>website design</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>the website has nice design</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>website usability</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>negative</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>The website is difficult to use. | The mobile experience is frustrating.</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The website is difficult to use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mobile experience</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The mobile experience is frustrating.</t>
         </is>
       </c>
     </row>
